--- a/Tables/AAR_trump.xlsx
+++ b/Tables/AAR_trump.xlsx
@@ -486,25 +486,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8437720422674784</v>
+        <v>0.652407887467172</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.4279688750380585</v>
+        <v>-0.7487672304706856</v>
       </c>
       <c r="D3" t="n">
-        <v>1.513233515275797</v>
+        <v>0.7320582079418859</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.056694670971486</v>
+        <v>-2.634169253366575</v>
       </c>
       <c r="F3" t="n">
-        <v>2.146483997943121</v>
+        <v>1.725319205668915</v>
       </c>
       <c r="G3" t="n">
-        <v>4.210699819792104</v>
+        <v>4.192783241246542</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.572654821113096</v>
+        <v>-1.542395202342314</v>
       </c>
     </row>
     <row r="4">
@@ -514,25 +514,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.653464920862139</v>
+        <v>2.170577714933287</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7350355390440216</v>
+        <v>0.8587122785204829</v>
       </c>
       <c r="D4" t="n">
-        <v>5.463983895374563</v>
+        <v>5.600403228965264</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.216979873852855</v>
+        <v>-0.5548363406524437</v>
       </c>
       <c r="F4" t="n">
-        <v>3.375461890922684</v>
+        <v>3.665951020186196</v>
       </c>
       <c r="G4" t="n">
-        <v>6.164947533700803</v>
+        <v>6.183563676705509</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5056723494397687</v>
+        <v>-0.2451508767584342</v>
       </c>
     </row>
   </sheetData>

--- a/Tables/AAR_trump.xlsx
+++ b/Tables/AAR_trump.xlsx
@@ -486,25 +486,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.652407887467172</v>
+        <v>0.6890512746656444</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.7487672304706856</v>
+        <v>-0.7637481724639331</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7320582079418859</v>
+        <v>0.7430696369945522</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.634169253366575</v>
+        <v>-2.627392358836814</v>
       </c>
       <c r="F3" t="n">
-        <v>1.725319205668915</v>
+        <v>1.729813697197707</v>
       </c>
       <c r="G3" t="n">
-        <v>4.192783241246542</v>
+        <v>4.161668927343864</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.542395202342314</v>
+        <v>-1.526828316039488</v>
       </c>
     </row>
     <row r="4">
@@ -514,25 +514,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.170577714933287</v>
+        <v>2.182164263701678</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8587122785204829</v>
+        <v>0.856919344732738</v>
       </c>
       <c r="D4" t="n">
-        <v>5.600403228965264</v>
+        <v>5.583677079706678</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5548363406524437</v>
+        <v>-0.5502891449366778</v>
       </c>
       <c r="F4" t="n">
-        <v>3.665951020186196</v>
+        <v>3.658780477924003</v>
       </c>
       <c r="G4" t="n">
-        <v>6.183563676705509</v>
+        <v>6.154835089382226</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2451508767584342</v>
+        <v>-0.2496189979610887</v>
       </c>
     </row>
   </sheetData>
